--- a/docs/功能测试用例.xlsx
+++ b/docs/功能测试用例.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="623">
   <si>
     <t>模块</t>
   </si>
@@ -496,13 +496,49 @@
     <t>接 TC-5.4</t>
   </si>
   <si>
-    <t>手动关工控机（不在保持窗口内）</t>
+    <t>手动关工控机（不在保持窗口内，且规则未要求开北斗）</t>
   </si>
   <si>
     <t>北斗随之关闭</t>
   </si>
   <si>
     <t>sensor_state 的 0x80 与 0x04 同时归 0</t>
+  </si>
+  <si>
+    <t>TC-5.7</t>
+  </si>
+  <si>
+    <t>规则直接开北斗</t>
+  </si>
+  <si>
+    <t>已校时，工控机关闭</t>
+  </si>
+  <si>
+    <t>下发“目标设备=北斗(0x04)”的规则并到点</t>
+  </si>
+  <si>
+    <t>北斗上电（规则可直接控制北斗）</t>
+  </si>
+  <si>
+    <t>sensor_state = 0x04（仅北斗开）</t>
+  </si>
+  <si>
+    <t>TC-5.8</t>
+  </si>
+  <si>
+    <t>多来源互不否决</t>
+  </si>
+  <si>
+    <t>接 TC-5.7</t>
+  </si>
+  <si>
+    <t>规则要求开北斗期间保持工控机关闭</t>
+  </si>
+  <si>
+    <t>北斗持续上电，不被跟随否决</t>
+  </si>
+  <si>
+    <t>sensor_state 持续保持 0x04</t>
   </si>
   <si>
     <t>TC-5.6</t>
@@ -3045,7 +3081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26.6363636363636" customWidth="1"/>
@@ -3770,7 +3806,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" ht="70" spans="1:11">
+    <row r="27" ht="98" spans="1:11">
       <c r="A27" s="2" t="s">
         <v>129</v>
       </c>
@@ -3808,67 +3844,67 @@
         <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" ht="112" spans="1:11">
+    <row r="29" ht="56" spans="1:11">
       <c r="A29" s="2" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" ht="70" spans="1:11">
+    <row r="30" ht="84" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>170</v>
@@ -3878,18 +3914,18 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" ht="70" spans="1:11">
+    <row r="31" ht="112" spans="1:11">
       <c r="A31" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>174</v>
@@ -3907,7 +3943,7 @@
     </row>
     <row r="32" ht="70" spans="1:11">
       <c r="A32" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>177</v>
@@ -3916,16 +3952,16 @@
         <v>178</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -3934,52 +3970,52 @@
     </row>
     <row r="33" ht="70" spans="1:11">
       <c r="A33" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" ht="84" spans="1:11">
+    <row r="34" ht="70" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -3988,25 +4024,25 @@
     </row>
     <row r="35" ht="70" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -4015,16 +4051,16 @@
     </row>
     <row r="36" ht="84" spans="1:11">
       <c r="A36" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>201</v>
@@ -4040,9 +4076,9 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" ht="112" spans="1:11">
+    <row r="37" ht="70" spans="1:11">
       <c r="A37" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>204</v>
@@ -4051,25 +4087,25 @@
         <v>205</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" ht="42" spans="1:11">
+    <row r="38" ht="84" spans="1:11">
       <c r="A38" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>210</v>
@@ -4078,88 +4114,88 @@
         <v>211</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" ht="70" spans="1:11">
+    <row r="39" ht="112" spans="1:11">
       <c r="A39" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>54</v>
+        <v>218</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" ht="56" spans="1:11">
+    <row r="40" ht="42" spans="1:11">
       <c r="A40" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" ht="238" spans="1:11">
+    <row r="41" ht="70" spans="1:11">
       <c r="A41" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>228</v>
+        <v>54</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>229</v>
@@ -4175,9 +4211,9 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" ht="84" spans="1:11">
+    <row r="42" ht="56" spans="1:11">
       <c r="A42" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>232</v>
@@ -4186,7 +4222,7 @@
         <v>233</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>234</v>
@@ -4202,27 +4238,27 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" ht="84" spans="1:11">
+    <row r="43" ht="238" spans="1:11">
       <c r="A43" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -4231,214 +4267,214 @@
     </row>
     <row r="44" ht="84" spans="1:11">
       <c r="A44" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" ht="42" spans="1:11">
+    <row r="45" ht="84" spans="1:11">
       <c r="A45" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" ht="210" spans="1:11">
+    <row r="46" ht="84" spans="1:11">
       <c r="A46" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" ht="98" spans="1:11">
+    <row r="47" ht="42" spans="1:11">
       <c r="A47" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" ht="126" spans="1:11">
+    <row r="48" ht="210" spans="1:11">
       <c r="A48" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" ht="56" spans="1:11">
+    <row r="49" ht="98" spans="1:11">
       <c r="A49" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" ht="56" spans="1:11">
+    <row r="50" ht="126" spans="1:11">
       <c r="A50" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" ht="84" spans="1:11">
+    <row r="51" ht="56" spans="1:11">
       <c r="A51" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -4447,7 +4483,7 @@
     </row>
     <row r="52" ht="56" spans="1:11">
       <c r="A52" s="2" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>283</v>
@@ -4456,10 +4492,10 @@
         <v>284</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>286</v>
@@ -4472,9 +4508,9 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" ht="42" spans="1:11">
+    <row r="53" ht="84" spans="1:11">
       <c r="A53" s="2" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>288</v>
@@ -4486,13 +4522,13 @@
         <v>290</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -4501,52 +4537,52 @@
     </row>
     <row r="54" ht="56" spans="1:11">
       <c r="A54" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" ht="84" spans="1:11">
+    <row r="55" ht="42" spans="1:11">
       <c r="A55" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="G55" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -4555,16 +4591,16 @@
     </row>
     <row r="56" ht="56" spans="1:11">
       <c r="A56" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>306</v>
@@ -4580,153 +4616,153 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" ht="42" spans="1:11">
+    <row r="57" ht="84" spans="1:11">
       <c r="A57" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" ht="42" spans="1:11">
+    <row r="58" ht="56" spans="1:11">
       <c r="A58" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" ht="56" spans="1:11">
+    <row r="59" ht="42" spans="1:11">
       <c r="A59" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" ht="84" spans="1:11">
+    <row r="60" ht="42" spans="1:11">
       <c r="A60" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" ht="42" spans="1:11">
+    <row r="61" ht="56" spans="1:11">
       <c r="A61" s="2" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" ht="70" spans="1:11">
+    <row r="62" ht="84" spans="1:11">
       <c r="A62" s="2" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>337</v>
@@ -4742,18 +4778,18 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" ht="112" spans="1:11">
+    <row r="63" ht="42" spans="1:11">
       <c r="A63" s="2" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>342</v>
+        <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>343</v>
@@ -4769,9 +4805,9 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" ht="56" spans="1:11">
+    <row r="64" ht="70" spans="1:11">
       <c r="A64" s="2" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>346</v>
@@ -4796,63 +4832,63 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" ht="126" spans="1:11">
+    <row r="65" ht="112" spans="1:11">
       <c r="A65" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" ht="70" spans="1:11">
+    <row r="66" ht="56" spans="1:11">
       <c r="A66" s="2" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" ht="56" spans="1:11">
+    <row r="67" ht="126" spans="1:11">
       <c r="A67" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>365</v>
@@ -4861,16 +4897,16 @@
         <v>366</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -4879,25 +4915,25 @@
     </row>
     <row r="68" ht="70" spans="1:11">
       <c r="A68" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -4906,16 +4942,16 @@
     </row>
     <row r="69" ht="56" spans="1:11">
       <c r="A69" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>379</v>
@@ -4931,9 +4967,9 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" ht="140" spans="1:11">
+    <row r="70" ht="70" spans="1:11">
       <c r="A70" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>382</v>
@@ -4942,25 +4978,25 @@
         <v>383</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" ht="42" spans="1:11">
+    <row r="71" ht="56" spans="1:11">
       <c r="A71" s="2" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>388</v>
@@ -4985,18 +5021,18 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" ht="84" spans="1:11">
+    <row r="72" ht="140" spans="1:11">
       <c r="A72" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>397</v>
@@ -5012,9 +5048,9 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" ht="70" spans="1:11">
+    <row r="73" ht="42" spans="1:11">
       <c r="A73" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>400</v>
@@ -5039,18 +5075,18 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" ht="70" spans="1:11">
+    <row r="74" ht="84" spans="1:11">
       <c r="A74" s="2" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>408</v>
+        <v>54</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>409</v>
@@ -5066,21 +5102,21 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" ht="42" spans="1:11">
+    <row r="75" ht="70" spans="1:11">
       <c r="A75" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>416</v>
@@ -5093,9 +5129,9 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" ht="98" spans="1:11">
+    <row r="76" ht="70" spans="1:11">
       <c r="A76" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>418</v>
@@ -5120,90 +5156,90 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" ht="70" spans="1:11">
+    <row r="77" ht="42" spans="1:11">
       <c r="A77" s="2" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>54</v>
+        <v>427</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" ht="42" spans="1:11">
+    <row r="78" ht="98" spans="1:11">
       <c r="A78" s="2" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" ht="56" spans="1:11">
+    <row r="79" ht="70" spans="1:11">
       <c r="A79" s="2" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>437</v>
+        <v>54</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" ht="70" spans="1:11">
+    <row r="80" ht="42" spans="1:11">
       <c r="A80" s="2" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>441</v>
@@ -5228,9 +5264,9 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" ht="42" spans="1:11">
+    <row r="81" ht="56" spans="1:11">
       <c r="A81" s="2" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>447</v>
@@ -5239,10 +5275,10 @@
         <v>448</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>450</v>
@@ -5255,27 +5291,27 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" ht="42" spans="1:11">
+    <row r="82" ht="70" spans="1:11">
       <c r="A82" s="2" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -5284,52 +5320,52 @@
     </row>
     <row r="83" ht="42" spans="1:11">
       <c r="A83" s="2" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" ht="28" spans="1:11">
+    <row r="84" ht="42" spans="1:11">
       <c r="A84" s="2" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -5338,30 +5374,84 @@
     </row>
     <row r="85" ht="42" spans="1:11">
       <c r="A85" s="2" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>54</v>
+        <v>455</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
+    </row>
+    <row r="86" ht="28" spans="1:11">
+      <c r="A86" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" ht="42" spans="1:11">
+      <c r="A87" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5383,13 +5473,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -5397,100 +5487,100 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C2" s="2">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" ht="70" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C3" s="2">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" ht="70" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" ht="70" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C5" s="2">
         <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" ht="70" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C6" s="2">
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" ht="84" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C7" s="2">
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" ht="56" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C8" s="2">
         <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -5514,41 +5604,41 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" ht="56" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B3" s="2">
         <v>4</v>
@@ -5557,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -5565,7 +5655,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -5574,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -5582,7 +5672,7 @@
     </row>
     <row r="5" ht="42" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B5" s="2">
         <v>6</v>
@@ -5591,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -5599,7 +5689,7 @@
     </row>
     <row r="6" ht="28" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B6" s="3">
         <v>46211</v>
@@ -5608,15 +5698,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B7" s="3">
         <v>46278</v>
@@ -5625,32 +5715,32 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -5659,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -5667,7 +5757,7 @@
     </row>
     <row r="10" ht="28" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B10" s="3">
         <v>46180</v>
@@ -5676,15 +5766,15 @@
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B11" s="2">
         <v>8</v>
@@ -5693,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E11" s="2">
         <v>9</v>
@@ -5701,7 +5791,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B12" s="2">
         <v>9</v>
@@ -5710,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E12" s="2">
         <v>15</v>
@@ -5718,7 +5808,7 @@
     </row>
     <row r="13" ht="28" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
@@ -5727,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
@@ -5735,7 +5825,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B14" s="2">
         <v>11</v>
@@ -5744,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -5752,7 +5842,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B15" s="2">
         <v>12</v>
@@ -5761,83 +5851,83 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" ht="56" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="17" ht="56" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" ht="70" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" ht="42" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" ht="42" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B20" s="2">
         <v>21</v>
@@ -5846,15 +5936,15 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B21" s="2">
         <v>22</v>
@@ -5863,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -5871,36 +5961,36 @@
     </row>
     <row r="22" ht="28" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C23" s="2">
         <v>5</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -5922,128 +6012,128 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" ht="56" spans="1:4">
@@ -6051,13 +6141,13 @@
         <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -6080,170 +6170,170 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" ht="42" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" ht="42" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/docs/功能测试用例.xlsx
+++ b/docs/功能测试用例.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="621">
   <si>
     <t>模块</t>
   </si>
@@ -340,10 +340,10 @@
     <t>发 $STR（35 条规则）</t>
   </si>
   <si>
-    <t>回 $ACK 且 error=00（成功）</t>
-  </si>
-  <si>
-    <t>$ACK: 24 41 43 4B 01 01 00 72 68 24 4F 56 45 52</t>
+    <t>无应答（属正常）；回读可确认生效</t>
+  </si>
+  <si>
+    <t>（无回复）；随后 $GETSTR 可读回新规则</t>
   </si>
   <si>
     <t>TC-4.2</t>
@@ -766,10 +766,10 @@
     <t>发 $READ 帧</t>
   </si>
   <si>
-    <t>回 14 字节 $ACK（成功）+ 30 字节 $STAR</t>
-  </si>
-  <si>
-    <t>$ACK: 24 41 43 4B 01 01 00 72 68 24 4F 56 45 52
+    <t>只回 30 字节 $STAR（无 $ACK）</t>
+  </si>
+  <si>
+    <t>$STAR: 24 53 54 41 52 01 EA 07 09 15 05 02 2B EE 00 03 01 04 01 25 01 04 00 CD 17 24 4F 56 45 52
 $STAR: 24 53 54 41 52 01 EA 07 09 15 05 02 2B EE 00 03 01 04 01 25 01 04 00 CD 17 24 4F 56 45 52</t>
   </si>
   <si>
@@ -782,7 +782,7 @@
     <t>发 $GETSTR 帧</t>
   </si>
   <si>
-    <t>回 $ACK + 222 字节 $STR</t>
+    <t>只回 222 字节 $STR（无 $ACK）</t>
   </si>
   <si>
     <t>$STR 共 222 字节，尾部 18 64 24 4F 56 45 52</t>
@@ -797,7 +797,7 @@
     <t>发 $STR 帧</t>
   </si>
   <si>
-    <t>回 $ACK 成功</t>
+    <t>无应答（正常）；规则已生效</t>
   </si>
   <si>
     <t>TC-8.4</t>
@@ -809,10 +809,10 @@
     <t>发 $REST 帧</t>
   </si>
   <si>
-    <t>回 $ACK 成功，约 300ms 后板子复位</t>
-  </si>
-  <si>
-    <t>$ACK 成功后板子重启，调试串口重新打印启动日志</t>
+    <t>无应答，约 300ms 后板子复位</t>
+  </si>
+  <si>
+    <t>板子重启，调试串口重新打印启动日志</t>
   </si>
   <si>
     <t>TC-8.5</t>
@@ -899,10 +899,10 @@
     <t>应答帧头</t>
   </si>
   <si>
-    <t>检查 $ACK 首 4 字节</t>
-  </si>
-  <si>
-    <t>必须为 $ACK（24 41 43 4B）</t>
+    <t>发坏 CRC 的帧，检查回复首 4 字节</t>
+  </si>
+  <si>
+    <t>必须为 $ACK（24 41 43 4B），仅异常时出现</t>
   </si>
   <si>
     <t>24 41 43 4B = '$ACK'</t>
@@ -941,7 +941,7 @@
     <t>正常收到应答</t>
   </si>
   <si>
-    <t>44 字节：$ACK + $STAR</t>
+    <t>30 字节：$STAR</t>
   </si>
   <si>
     <t>TC-9.2</t>
@@ -986,10 +986,7 @@
     <t>从 LoRa 发 $READ 帧</t>
   </si>
   <si>
-    <t>收到 $ACK + $STAR</t>
-  </si>
-  <si>
-    <t>44 字节：$ACK(14) + $STAR(30)</t>
+    <t>收到 $STAR</t>
   </si>
   <si>
     <t>TC-10.2</t>
@@ -1058,10 +1055,7 @@
     <t>从 LoRa 发 $STR</t>
   </si>
   <si>
-    <t>回 $ACK 成功，规则生效</t>
-  </si>
-  <si>
-    <t>$ACK error=00；$GETSTR 可回读新规则</t>
+    <t>$GETSTR 可回读新规则</t>
   </si>
   <si>
     <t>手动控制</t>
@@ -4238,7 +4232,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" ht="238" spans="1:11">
+    <row r="43" ht="308" spans="1:11">
       <c r="A43" s="2" t="s">
         <v>237</v>
       </c>
@@ -4319,7 +4313,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" ht="84" spans="1:11">
+    <row r="46" ht="70" spans="1:11">
       <c r="A46" s="2" t="s">
         <v>237</v>
       </c>
@@ -4481,7 +4475,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" ht="56" spans="1:11">
+    <row r="52" ht="84" spans="1:11">
       <c r="A52" s="2" t="s">
         <v>237</v>
       </c>
@@ -4636,7 +4630,7 @@
         <v>314</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -4648,22 +4642,22 @@
         <v>309</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -4675,19 +4669,19 @@
         <v>309</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>262</v>
@@ -4702,22 +4696,22 @@
         <v>309</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -4729,49 +4723,49 @@
         <v>309</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" ht="84" spans="1:11">
+    <row r="62" ht="56" spans="1:11">
       <c r="A62" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -4780,25 +4774,25 @@
     </row>
     <row r="63" ht="42" spans="1:11">
       <c r="A63" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -4807,25 +4801,25 @@
     </row>
     <row r="64" ht="70" spans="1:11">
       <c r="A64" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="G64" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -4834,25 +4828,25 @@
     </row>
     <row r="65" ht="112" spans="1:11">
       <c r="A65" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -4861,25 +4855,25 @@
     </row>
     <row r="66" ht="56" spans="1:11">
       <c r="A66" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -4888,25 +4882,25 @@
     </row>
     <row r="67" ht="126" spans="1:11">
       <c r="A67" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="G67" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -4915,25 +4909,25 @@
     </row>
     <row r="68" ht="70" spans="1:11">
       <c r="A68" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -4942,25 +4936,25 @@
     </row>
     <row r="69" ht="56" spans="1:11">
       <c r="A69" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="F69" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -4969,25 +4963,25 @@
     </row>
     <row r="70" ht="70" spans="1:11">
       <c r="A70" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -4996,25 +4990,25 @@
     </row>
     <row r="71" ht="56" spans="1:11">
       <c r="A71" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="G71" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -5023,25 +5017,25 @@
     </row>
     <row r="72" ht="140" spans="1:11">
       <c r="A72" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="F72" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="G72" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -5050,25 +5044,25 @@
     </row>
     <row r="73" ht="42" spans="1:11">
       <c r="A73" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -5077,25 +5071,25 @@
     </row>
     <row r="74" ht="84" spans="1:11">
       <c r="A74" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E74" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -5104,25 +5098,25 @@
     </row>
     <row r="75" ht="70" spans="1:11">
       <c r="A75" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="G75" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -5131,25 +5125,25 @@
     </row>
     <row r="76" ht="70" spans="1:11">
       <c r="A76" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -5158,25 +5152,25 @@
     </row>
     <row r="77" ht="42" spans="1:11">
       <c r="A77" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="E77" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="G77" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -5185,25 +5179,25 @@
     </row>
     <row r="78" ht="98" spans="1:11">
       <c r="A78" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -5212,25 +5206,25 @@
     </row>
     <row r="79" ht="70" spans="1:11">
       <c r="A79" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -5239,25 +5233,25 @@
     </row>
     <row r="80" ht="42" spans="1:11">
       <c r="A80" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="G80" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -5266,25 +5260,25 @@
     </row>
     <row r="81" ht="56" spans="1:11">
       <c r="A81" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="E81" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="G81" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -5293,25 +5287,25 @@
     </row>
     <row r="82" ht="70" spans="1:11">
       <c r="A82" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="G82" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -5320,25 +5314,25 @@
     </row>
     <row r="83" ht="42" spans="1:11">
       <c r="A83" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="F83" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E83" s="2" t="s">
+      <c r="G83" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -5347,25 +5341,25 @@
     </row>
     <row r="84" ht="42" spans="1:11">
       <c r="A84" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="F84" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E84" s="2" t="s">
+      <c r="G84" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -5374,25 +5368,25 @@
     </row>
     <row r="85" ht="42" spans="1:11">
       <c r="A85" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -5401,25 +5395,25 @@
     </row>
     <row r="86" ht="28" spans="1:11">
       <c r="A86" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E86" s="2" t="s">
+      <c r="G86" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -5428,25 +5422,25 @@
     </row>
     <row r="87" ht="42" spans="1:11">
       <c r="A87" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E87" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
@@ -5473,13 +5467,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -5487,94 +5481,94 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C2" s="2">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" ht="70" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C3" s="2">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" ht="70" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" ht="70" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C5" s="2">
         <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" ht="70" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C6" s="2">
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="84" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C7" s="2">
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" ht="56" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C8" s="2">
         <v>22</v>
@@ -5604,41 +5598,41 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" ht="56" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B3" s="2">
         <v>4</v>
@@ -5647,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -5655,7 +5649,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -5664,7 +5658,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -5672,7 +5666,7 @@
     </row>
     <row r="5" ht="42" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B5" s="2">
         <v>6</v>
@@ -5681,7 +5675,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -5689,7 +5683,7 @@
     </row>
     <row r="6" ht="28" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B6" s="3">
         <v>46211</v>
@@ -5698,15 +5692,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B7" s="3">
         <v>46278</v>
@@ -5715,32 +5709,32 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -5749,7 +5743,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -5757,7 +5751,7 @@
     </row>
     <row r="10" ht="28" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B10" s="3">
         <v>46180</v>
@@ -5766,15 +5760,15 @@
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B11" s="2">
         <v>8</v>
@@ -5783,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E11" s="2">
         <v>9</v>
@@ -5791,7 +5785,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B12" s="2">
         <v>9</v>
@@ -5800,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E12" s="2">
         <v>15</v>
@@ -5808,7 +5802,7 @@
     </row>
     <row r="13" ht="28" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
@@ -5817,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
@@ -5825,7 +5819,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B14" s="2">
         <v>11</v>
@@ -5834,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -5842,7 +5836,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B15" s="2">
         <v>12</v>
@@ -5851,83 +5845,83 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" ht="56" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" ht="56" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18" ht="70" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" ht="42" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" ht="42" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B20" s="2">
         <v>21</v>
@@ -5936,15 +5930,15 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B21" s="2">
         <v>22</v>
@@ -5953,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -5961,36 +5955,36 @@
     </row>
     <row r="22" ht="28" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C23" s="2">
         <v>5</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -6012,128 +6006,128 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="10" ht="56" spans="1:4">
@@ -6141,13 +6135,13 @@
         <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -6170,170 +6164,170 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" ht="42" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="11" ht="42" spans="1:4">
       <c r="A11" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:4">
       <c r="A12" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/docs/功能测试用例.xlsx
+++ b/docs/功能测试用例.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="623">
   <si>
     <t>模块</t>
   </si>
@@ -340,10 +340,10 @@
     <t>发 $STR（35 条规则）</t>
   </si>
   <si>
-    <t>无应答（属正常）；回读可确认生效</t>
-  </si>
-  <si>
-    <t>（无回复）；随后 $GETSTR 可读回新规则</t>
+    <t>回 $ACK 且 error=00（成功）</t>
+  </si>
+  <si>
+    <t>$ACK: 24 41 43 4B 01 01 00 72 68 24 4F 56 45 52</t>
   </si>
   <si>
     <t>TC-4.2</t>
@@ -766,10 +766,10 @@
     <t>发 $READ 帧</t>
   </si>
   <si>
-    <t>只回 30 字节 $STAR（无 $ACK）</t>
-  </si>
-  <si>
-    <t>$STAR: 24 53 54 41 52 01 EA 07 09 15 05 02 2B EE 00 03 01 04 01 25 01 04 00 CD 17 24 4F 56 45 52
+    <t>回 14 字节 $ACK（成功）+ 30 字节 $STAR</t>
+  </si>
+  <si>
+    <t>$ACK: 24 41 43 4B 01 01 00 72 68 24 4F 56 45 52
 $STAR: 24 53 54 41 52 01 EA 07 09 15 05 02 2B EE 00 03 01 04 01 25 01 04 00 CD 17 24 4F 56 45 52</t>
   </si>
   <si>
@@ -782,7 +782,7 @@
     <t>发 $GETSTR 帧</t>
   </si>
   <si>
-    <t>只回 222 字节 $STR（无 $ACK）</t>
+    <t>回 $ACK + 222 字节 $STR</t>
   </si>
   <si>
     <t>$STR 共 222 字节，尾部 18 64 24 4F 56 45 52</t>
@@ -797,7 +797,7 @@
     <t>发 $STR 帧</t>
   </si>
   <si>
-    <t>无应答（正常）；规则已生效</t>
+    <t>回 $ACK 成功</t>
   </si>
   <si>
     <t>TC-8.4</t>
@@ -809,10 +809,10 @@
     <t>发 $REST 帧</t>
   </si>
   <si>
-    <t>无应答，约 300ms 后板子复位</t>
-  </si>
-  <si>
-    <t>板子重启，调试串口重新打印启动日志</t>
+    <t>回 $ACK 成功，约 300ms 后板子复位</t>
+  </si>
+  <si>
+    <t>$ACK 成功后板子重启，调试串口重新打印启动日志</t>
   </si>
   <si>
     <t>TC-8.5</t>
@@ -899,10 +899,10 @@
     <t>应答帧头</t>
   </si>
   <si>
-    <t>发坏 CRC 的帧，检查回复首 4 字节</t>
-  </si>
-  <si>
-    <t>必须为 $ACK（24 41 43 4B），仅异常时出现</t>
+    <t>检查 $ACK 首 4 字节</t>
+  </si>
+  <si>
+    <t>必须为 $ACK（24 41 43 4B）</t>
   </si>
   <si>
     <t>24 41 43 4B = '$ACK'</t>
@@ -941,7 +941,7 @@
     <t>正常收到应答</t>
   </si>
   <si>
-    <t>30 字节：$STAR</t>
+    <t>44 字节：$ACK + $STAR</t>
   </si>
   <si>
     <t>TC-9.2</t>
@@ -986,7 +986,10 @@
     <t>从 LoRa 发 $READ 帧</t>
   </si>
   <si>
-    <t>收到 $STAR</t>
+    <t>收到 $ACK + $STAR</t>
+  </si>
+  <si>
+    <t>44 字节：$ACK(14) + $STAR(30)</t>
   </si>
   <si>
     <t>TC-10.2</t>
@@ -1055,7 +1058,10 @@
     <t>从 LoRa 发 $STR</t>
   </si>
   <si>
-    <t>$GETSTR 可回读新规则</t>
+    <t>回 $ACK 成功，规则生效</t>
+  </si>
+  <si>
+    <t>$ACK error=00；$GETSTR 可回读新规则</t>
   </si>
   <si>
     <t>手动控制</t>
@@ -4232,7 +4238,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" ht="308" spans="1:11">
+    <row r="43" ht="238" spans="1:11">
       <c r="A43" s="2" t="s">
         <v>237</v>
       </c>
@@ -4313,7 +4319,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" ht="70" spans="1:11">
+    <row r="46" ht="84" spans="1:11">
       <c r="A46" s="2" t="s">
         <v>237</v>
       </c>
@@ -4475,7 +4481,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" ht="84" spans="1:11">
+    <row r="52" ht="56" spans="1:11">
       <c r="A52" s="2" t="s">
         <v>237</v>
       </c>
@@ -4630,7 +4636,7 @@
         <v>314</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -4642,22 +4648,22 @@
         <v>309</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -4669,19 +4675,19 @@
         <v>309</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>262</v>
@@ -4696,22 +4702,22 @@
         <v>309</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -4723,49 +4729,49 @@
         <v>309</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" ht="56" spans="1:11">
+    <row r="62" ht="84" spans="1:11">
       <c r="A62" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>252</v>
+        <v>338</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -4774,25 +4780,25 @@
     </row>
     <row r="63" ht="42" spans="1:11">
       <c r="A63" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -4801,25 +4807,25 @@
     </row>
     <row r="64" ht="70" spans="1:11">
       <c r="A64" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -4828,25 +4834,25 @@
     </row>
     <row r="65" ht="112" spans="1:11">
       <c r="A65" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -4855,25 +4861,25 @@
     </row>
     <row r="66" ht="56" spans="1:11">
       <c r="A66" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -4882,25 +4888,25 @@
     </row>
     <row r="67" ht="126" spans="1:11">
       <c r="A67" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -4909,25 +4915,25 @@
     </row>
     <row r="68" ht="70" spans="1:11">
       <c r="A68" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -4936,25 +4942,25 @@
     </row>
     <row r="69" ht="56" spans="1:11">
       <c r="A69" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -4963,25 +4969,25 @@
     </row>
     <row r="70" ht="70" spans="1:11">
       <c r="A70" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -4990,25 +4996,25 @@
     </row>
     <row r="71" ht="56" spans="1:11">
       <c r="A71" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -5017,25 +5023,25 @@
     </row>
     <row r="72" ht="140" spans="1:11">
       <c r="A72" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -5044,25 +5050,25 @@
     </row>
     <row r="73" ht="42" spans="1:11">
       <c r="A73" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -5071,25 +5077,25 @@
     </row>
     <row r="74" ht="84" spans="1:11">
       <c r="A74" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -5098,25 +5104,25 @@
     </row>
     <row r="75" ht="70" spans="1:11">
       <c r="A75" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -5125,25 +5131,25 @@
     </row>
     <row r="76" ht="70" spans="1:11">
       <c r="A76" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -5152,25 +5158,25 @@
     </row>
     <row r="77" ht="42" spans="1:11">
       <c r="A77" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -5179,25 +5185,25 @@
     </row>
     <row r="78" ht="98" spans="1:11">
       <c r="A78" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -5206,25 +5212,25 @@
     </row>
     <row r="79" ht="70" spans="1:11">
       <c r="A79" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -5233,25 +5239,25 @@
     </row>
     <row r="80" ht="42" spans="1:11">
       <c r="A80" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -5260,25 +5266,25 @@
     </row>
     <row r="81" ht="56" spans="1:11">
       <c r="A81" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -5287,25 +5293,25 @@
     </row>
     <row r="82" ht="70" spans="1:11">
       <c r="A82" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -5314,25 +5320,25 @@
     </row>
     <row r="83" ht="42" spans="1:11">
       <c r="A83" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -5341,25 +5347,25 @@
     </row>
     <row r="84" ht="42" spans="1:11">
       <c r="A84" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -5368,25 +5374,25 @@
     </row>
     <row r="85" ht="42" spans="1:11">
       <c r="A85" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -5395,25 +5401,25 @@
     </row>
     <row r="86" ht="28" spans="1:11">
       <c r="A86" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -5422,25 +5428,25 @@
     </row>
     <row r="87" ht="42" spans="1:11">
       <c r="A87" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
@@ -5467,13 +5473,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -5481,94 +5487,94 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C2" s="2">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" ht="70" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C3" s="2">
         <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" ht="70" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" ht="70" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C5" s="2">
         <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" ht="70" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C6" s="2">
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" ht="84" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C7" s="2">
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" ht="56" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C8" s="2">
         <v>22</v>
@@ -5598,41 +5604,41 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" ht="56" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B3" s="2">
         <v>4</v>
@@ -5641,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -5649,7 +5655,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -5658,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -5666,7 +5672,7 @@
     </row>
     <row r="5" ht="42" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B5" s="2">
         <v>6</v>
@@ -5675,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -5683,7 +5689,7 @@
     </row>
     <row r="6" ht="28" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B6" s="3">
         <v>46211</v>
@@ -5692,15 +5698,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B7" s="3">
         <v>46278</v>
@@ -5709,32 +5715,32 @@
         <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -5743,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -5751,7 +5757,7 @@
     </row>
     <row r="10" ht="28" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B10" s="3">
         <v>46180</v>
@@ -5760,15 +5766,15 @@
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B11" s="2">
         <v>8</v>
@@ -5777,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E11" s="2">
         <v>9</v>
@@ -5785,7 +5791,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B12" s="2">
         <v>9</v>
@@ -5794,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E12" s="2">
         <v>15</v>
@@ -5802,7 +5808,7 @@
     </row>
     <row r="13" ht="28" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
@@ -5811,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
@@ -5819,7 +5825,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B14" s="2">
         <v>11</v>
@@ -5828,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -5836,7 +5842,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B15" s="2">
         <v>12</v>
@@ -5845,83 +5851,83 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" ht="56" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="17" ht="56" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" ht="70" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" ht="42" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" ht="42" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B20" s="2">
         <v>21</v>
@@ -5930,15 +5936,15 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B21" s="2">
         <v>22</v>
@@ -5947,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -5955,36 +5961,36 @@
     </row>
     <row r="22" ht="28" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C23" s="2">
         <v>5</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -6006,128 +6012,128 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" ht="56" spans="1:4">
@@ -6135,13 +6141,13 @@
         <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -6164,170 +6170,170 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>588</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" ht="42" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" ht="42" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/docs/功能测试用例.xlsx
+++ b/docs/功能测试用例.xlsx
@@ -839,10 +839,10 @@
     <t>发一帧故意改坏 CRC 的 $READ</t>
   </si>
   <si>
-    <t>回 $ACK 且 error=01（失败）</t>
-  </si>
-  <si>
-    <t>$ACK: 24 41 43 4B 01 01 01 B3 A8 24 4F 56 45 52（第 7 字节 01 = 失败）
+    <t>无任何应答（帧被丢弃）</t>
+  </si>
+  <si>
+    <t>（无回复）；调试口记录“校验失败”告警日志（第 7 字节 01 = 失败）
 [WARN ] Protocol: 校验失败：收到 0xFFFF，计算 0xEB08</t>
   </si>
   <si>
@@ -4373,7 +4373,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" ht="210" spans="1:11">
+    <row r="48" ht="224" spans="1:11">
       <c r="A48" s="2" t="s">
         <v>237</v>
       </c>
